--- a/data/trans_dic/P16A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 10,5</t>
+          <t>7,01; 10,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,61</t>
+          <t>9,0; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,32</t>
+          <t>8,83; 13,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,55</t>
+          <t>15,62; 21,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,46; 19,79</t>
+          <t>15,35; 19,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,23</t>
+          <t>22,15; 27,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,9; 28,33</t>
+          <t>22,65; 28,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,06; 37,58</t>
+          <t>31,83; 37,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 14,9</t>
+          <t>12,19; 15,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 20,68</t>
+          <t>17,41; 20,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 21,3</t>
+          <t>17,46; 21,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 30,16</t>
+          <t>25,88; 29,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,86</t>
+          <t>2,23; 3,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,9</t>
+          <t>3,92; 6,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,21</t>
+          <t>4,25; 6,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,85</t>
+          <t>4,35; 7,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,8</t>
+          <t>6,33; 8,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 12,76</t>
+          <t>9,71; 12,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,92</t>
+          <t>11,06; 14,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 14,68</t>
+          <t>9,41; 14,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,94</t>
+          <t>4,4; 5,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,81</t>
+          <t>6,96; 8,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 9,66</t>
+          <t>7,79; 9,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 10,77</t>
+          <t>7,53; 10,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,67</t>
+          <t>2,27; 5,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,8</t>
+          <t>2,75; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,09</t>
+          <t>2,47; 5,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,07</t>
+          <t>4,56; 8,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,64</t>
+          <t>4,28; 8,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,82</t>
+          <t>3,91; 8,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,65</t>
+          <t>4,16; 8,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,73</t>
+          <t>7,09; 10,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,44</t>
+          <t>3,69; 6,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,52</t>
+          <t>4,02; 7,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,6</t>
+          <t>3,75; 6,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,73</t>
+          <t>6,3; 8,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,75</t>
+          <t>4,2; 5,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 7,57</t>
+          <t>5,77; 7,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,15</t>
+          <t>5,46; 7,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,33</t>
+          <t>6,3; 9,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 12,25</t>
+          <t>10,06; 12,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,35; 16,91</t>
+          <t>14,43; 16,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 16,43</t>
+          <t>13,94; 16,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 18,12</t>
+          <t>13,23; 17,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,85</t>
+          <t>7,51; 8,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,31; 11,95</t>
+          <t>10,44; 12,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 11,59</t>
+          <t>10,11; 11,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 13,48</t>
+          <t>10,78; 13,46</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74219; 108345</t>
+          <t>72358; 108689</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90038; 132616</t>
+          <t>87705; 128142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67629; 100478</t>
+          <t>66592; 101028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79059; 110993</t>
+          <t>80425; 112456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>203297; 260261</t>
+          <t>201916; 256261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>300747; 364330</t>
+          <t>296353; 365049</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>227825; 281746</t>
+          <t>225276; 284686</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>242213; 283921</t>
+          <t>240442; 282522</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>284794; 349734</t>
+          <t>286055; 355043</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>402579; 478259</t>
+          <t>402505; 481934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303078; 372499</t>
+          <t>305392; 370880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>329725; 383153</t>
+          <t>328814; 379360</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37403; 65347</t>
+          <t>37720; 64674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75237; 115918</t>
+          <t>76958; 117847</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87633; 128864</t>
+          <t>88152; 129476</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105719; 179875</t>
+          <t>99742; 178854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>98214; 139764</t>
+          <t>100513; 140221</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>170620; 224291</t>
+          <t>170728; 224140</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>218557; 276760</t>
+          <t>219899; 281469</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>201134; 328586</t>
+          <t>210534; 324229</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>145821; 194977</t>
+          <t>144356; 195324</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>258249; 328004</t>
+          <t>259065; 324719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>318539; 392746</t>
+          <t>316664; 391820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>339690; 487722</t>
+          <t>340825; 488322</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13296; 31250</t>
+          <t>12527; 31772</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13491; 37544</t>
+          <t>13220; 35726</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12658; 33305</t>
+          <t>13499; 32451</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28887; 52190</t>
+          <t>29474; 53606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20322; 41156</t>
+          <t>20413; 40326</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17998; 40429</t>
+          <t>17922; 39488</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23080; 47510</t>
+          <t>22832; 48514</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48242; 70881</t>
+          <t>46844; 71056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38006; 66148</t>
+          <t>37922; 66864</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37675; 70679</t>
+          <t>37825; 68262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40722; 72339</t>
+          <t>41055; 71693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82649; 114134</t>
+          <t>82377; 115503</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>137978; 188322</t>
+          <t>137711; 186644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>195611; 258811</t>
+          <t>197351; 259778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184826; 241585</t>
+          <t>184321; 240273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222511; 321920</t>
+          <t>217547; 319352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>341295; 413853</t>
+          <t>339971; 408540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>509919; 601067</t>
+          <t>512767; 597227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>493571; 580425</t>
+          <t>492334; 579417</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>481978; 662028</t>
+          <t>483402; 655027</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>495709; 588787</t>
+          <t>499543; 582131</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>719190; 833413</t>
+          <t>727853; 837201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>692256; 800989</t>
+          <t>698697; 808029</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>763101; 957660</t>
+          <t>765729; 956560</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,53</t>
+          <t>7,14; 10,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,15</t>
+          <t>9,1; 13,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,39</t>
+          <t>9,01; 13,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,62; 21,84</t>
+          <t>14,7; 20,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 19,49</t>
+          <t>15,34; 19,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,15; 27,29</t>
+          <t>22,55; 27,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,65; 28,62</t>
+          <t>22,68; 28,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,83; 37,39</t>
+          <t>31,39; 36,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 15,13</t>
+          <t>12,11; 14,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 20,84</t>
+          <t>17,26; 20,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 21,21</t>
+          <t>17,42; 21,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,88; 29,86</t>
+          <t>25,29; 29,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,82</t>
+          <t>2,15; 3,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,0</t>
+          <t>3,88; 5,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,24</t>
+          <t>4,24; 6,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,81</t>
+          <t>6,36; 8,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,83</t>
+          <t>6,26; 8,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 12,75</t>
+          <t>9,72; 12,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 14,16</t>
+          <t>11,05; 14,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,49</t>
+          <t>12,96; 15,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,95</t>
+          <t>4,47; 6,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 8,72</t>
+          <t>6,83; 8,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,64</t>
+          <t>7,88; 9,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 10,78</t>
+          <t>9,88; 11,65</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,76</t>
+          <t>2,42; 5,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,42</t>
+          <t>2,71; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,93</t>
+          <t>2,41; 5,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,29</t>
+          <t>4,2; 7,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,46</t>
+          <t>4,22; 8,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,61</t>
+          <t>3,91; 8,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,83</t>
+          <t>4,18; 8,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,76</t>
+          <t>7,17; 10,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,51</t>
+          <t>3,6; 6,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,26</t>
+          <t>4,03; 7,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,54</t>
+          <t>3,63; 6,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,84</t>
+          <t>6,2; 8,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,7</t>
+          <t>4,14; 5,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,6</t>
+          <t>5,72; 7,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,11</t>
+          <t>5,41; 7,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,25</t>
+          <t>7,81; 9,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 12,09</t>
+          <t>10,14; 12,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 16,8</t>
+          <t>14,27; 16,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 16,4</t>
+          <t>13,89; 16,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,23; 17,93</t>
+          <t>16,42; 18,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,75</t>
+          <t>7,44; 8,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 12,0</t>
+          <t>10,39; 12,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 11,69</t>
+          <t>10,09; 11,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 13,46</t>
+          <t>12,5; 13,86</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93817</t>
+          <t>100923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>261106</t>
+          <t>280074</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>354923</t>
+          <t>380997</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72358; 108689</t>
+          <t>73646; 108631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87705; 128142</t>
+          <t>88704; 131612</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66592; 101028</t>
+          <t>67950; 99630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80425; 112456</t>
+          <t>85038; 119392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>201916; 256261</t>
+          <t>201762; 259104</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>296353; 365049</t>
+          <t>301715; 364152</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>225276; 284686</t>
+          <t>225559; 283717</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>240442; 282522</t>
+          <t>258078; 300348</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>286055; 355043</t>
+          <t>284219; 351606</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>402505; 481934</t>
+          <t>399111; 475925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305392; 370880</t>
+          <t>304626; 369641</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>328814; 379360</t>
+          <t>354250; 410127</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149457</t>
+          <t>163430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>281750</t>
+          <t>307161</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>431208</t>
+          <t>470591</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37720; 64674</t>
+          <t>36386; 65495</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76958; 117847</t>
+          <t>76103; 115282</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88152; 129476</t>
+          <t>87996; 130411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99742; 178854</t>
+          <t>141858; 190535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100513; 140221</t>
+          <t>99458; 141699</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>170728; 224140</t>
+          <t>170784; 226181</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>219899; 281469</t>
+          <t>219713; 278482</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>210534; 324229</t>
+          <t>281483; 332229</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>144356; 195324</t>
+          <t>146793; 198587</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>259065; 324719</t>
+          <t>254111; 324283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>316664; 391820</t>
+          <t>320301; 393669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>340825; 488322</t>
+          <t>434883; 512865</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>40958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58597</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97924</t>
+          <t>105527</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12527; 31772</t>
+          <t>13369; 30511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13220; 35726</t>
+          <t>13026; 36920</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13499; 32451</t>
+          <t>13200; 32708</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29474; 53606</t>
+          <t>29913; 54393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20413; 40326</t>
+          <t>20103; 40403</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17922; 39488</t>
+          <t>17919; 40488</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22832; 48514</t>
+          <t>22955; 46908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46844; 71056</t>
+          <t>52688; 78290</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37922; 66864</t>
+          <t>37004; 65389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37825; 68262</t>
+          <t>37884; 67817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41055; 71693</t>
+          <t>39828; 73485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82377; 115503</t>
+          <t>89710; 124034</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>601452</t>
+          <t>651804</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>884054</t>
+          <t>957114</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>137711; 186644</t>
+          <t>135663; 187471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197351; 259778</t>
+          <t>195546; 260016</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184321; 240273</t>
+          <t>182632; 239783</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>217547; 319352</t>
+          <t>274973; 339911</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>339971; 408540</t>
+          <t>342761; 412231</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>512767; 597227</t>
+          <t>507017; 598890</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>492334; 579417</t>
+          <t>490598; 580699</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>483402; 655027</t>
+          <t>612139; 690130</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>499543; 582131</t>
+          <t>495382; 586238</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>727853; 837201</t>
+          <t>724288; 839033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>698697; 808029</t>
+          <t>696971; 801868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>765729; 956560</t>
+          <t>906101; 1004505</t>
         </is>
       </c>
     </row>
